--- a/artfynd/A 25843-2021 artfynd.xlsx
+++ b/artfynd/A 25843-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 25843-2021 artfynd.xlsx
+++ b/artfynd/A 25843-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1845,6 +1845,133 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118099571</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Örbäck, 1 km SO om (knärot)Öst, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>563501</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6649884</v>
+      </c>
+      <c r="S11" t="n">
+        <v>30</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norberg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Karbenning</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>U-Nor-0271</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>En planta med blomstjälk i knopp.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Källberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Källberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25843-2021 artfynd.xlsx
+++ b/artfynd/A 25843-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1972,6 +1972,135 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>118114381</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104931</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gammelskogen Örbäck, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>563442</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6649809</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norberg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Karbenning</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-29</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Källberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Källberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25843-2021 artfynd.xlsx
+++ b/artfynd/A 25843-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1847,10 +1847,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118099571</v>
+        <v>118114381</v>
       </c>
       <c r="B11" t="n">
-        <v>97846</v>
+        <v>104940</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1859,51 +1859,57 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örbäck, 1 km SO om (knärot)Öst, Vstm</t>
+          <t>Gammelskogen Örbäck, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>563501</v>
+        <v>563442</v>
       </c>
       <c r="R11" t="n">
-        <v>6649884</v>
+        <v>6649809</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1925,24 +1931,24 @@
           <t>Karbenning</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>U-Nor-0271</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
           <t>2024-06-29</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-06-29</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>En planta med blomstjälk i knopp.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1966,140 +1972,7 @@
           <t>Anders Källberg</t>
         </is>
       </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>118114381</v>
-      </c>
-      <c r="B12" t="n">
-        <v>104940</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Gammelskogen Örbäck, Vstm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>563442</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6649809</v>
-      </c>
-      <c r="S12" t="n">
-        <v>25</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Norberg</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Karbenning</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-06-29</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Anders Källberg</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Anders Källberg</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
